--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104541_W10.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104541_W10.xlsx
@@ -565,58 +565,58 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4081</v>
+        <v>2.6738</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7227</v>
+        <v>1.9531</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6855</v>
+        <v>0.7207</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7068</v>
+        <v>1.7017</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1097</v>
+        <v>1.106</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5971</v>
+        <v>0.5958</v>
       </c>
       <c r="J2" t="n">
-        <v>1.7227</v>
+        <v>1.7162</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1256</v>
+        <v>1.1204</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5971</v>
+        <v>0.5958</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0209</v>
+        <v>0.2892</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>0.2369</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0209</v>
+        <v>0.0523</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7204</v>
+        <v>2.3629</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5442</v>
+        <v>5.0001</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.8238</v>
+        <v>-2.6371</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2448</v>
+        <v>-0.2328</v>
       </c>
       <c r="H3" t="n">
-        <v>0.163</v>
+        <v>0.1691</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4078</v>
+        <v>-0.4019</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0726</v>
+        <v>3.0629</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2814</v>
+        <v>1.2755</v>
       </c>
       <c r="L3" t="n">
-        <v>1.7912</v>
+        <v>1.7874</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.3175</v>
+        <v>-3.2957</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1185</v>
+        <v>-1.1064</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.199</v>
+        <v>-2.1893</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1689</v>
+        <v>-0.5424</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4869</v>
+        <v>-0.0141</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.5283</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6402</v>
+        <v>1.0529</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6912</v>
+        <v>3.0101</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.0509</v>
+        <v>-1.9572</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.1513</v>
+        <v>-3.1492</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.277</v>
+        <v>-2.2748</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8743</v>
+        <v>-0.8744</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5443</v>
+        <v>0.5201</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.3086</v>
+        <v>-0.321</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8529</v>
+        <v>0.8411</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.6956</v>
+        <v>-3.6693</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.9684</v>
+        <v>-1.9538</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.7272</v>
+        <v>-1.7155</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3011</v>
+        <v>-0.8874</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9043</v>
+        <v>-0.5508</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3968</v>
+        <v>-0.3366</v>
       </c>
       <c r="V4" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="W4" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. BRANKOVIC</t>
+          <t>F. ALONSO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2045</v>
+        <v>-0.1567</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4107</v>
+        <v>-0.3166</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6152</v>
+        <v>0.1599</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.0254</v>
+        <v>-2.1624</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.0792</v>
+        <v>-0.3019</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9462</v>
+        <v>-1.8605</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5874</v>
+        <v>-0.7879</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.662</v>
+        <v>0.1584</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0746</v>
+        <v>-0.9463</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.438</v>
+        <v>-1.3745</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4171</v>
+        <v>-0.4603</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0209</v>
+        <v>-0.9143</v>
       </c>
       <c r="P5" t="n">
-        <v>1.361</v>
+        <v>2.0487</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2268</v>
+        <v>-0.4553</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5878</v>
+        <v>2.5039</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4599</v>
+        <v>-0.7455000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2249</v>
+        <v>-0.3207</v>
       </c>
       <c r="U5" t="n">
-        <v>0.235</v>
+        <v>-0.4248</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="6">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2459</v>
+        <v>-0.9399</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4517</v>
+        <v>0.7963</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.6976</v>
+        <v>-1.7362</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6842</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4589</v>
+        <v>1.4563</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.1431</v>
+        <v>-2.1405</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7965</v>
+        <v>1.7814</v>
       </c>
       <c r="K6" t="n">
-        <v>2.5456</v>
+        <v>2.5338</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.4807</v>
+        <v>-2.4656</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0867</v>
+        <v>-1.0775</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.394</v>
+        <v>-1.3881</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0773</v>
+        <v>0.3785</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0162</v>
+        <v>0.3807</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0611</v>
+        <v>-0.0022</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. ALONSO</t>
+          <t>D. BRANKOVIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.53</v>
+        <v>-1.2461</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5986</v>
+        <v>-0.4312</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06859999999999999</v>
+        <v>-0.8149</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.168</v>
+        <v>-3.0288</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3074</v>
+        <v>-2.0875</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.8605</v>
+        <v>-0.9412</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7723</v>
+        <v>-0.6052</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1661</v>
+        <v>-0.6797</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.9383</v>
+        <v>0.0745</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3957</v>
+        <v>-2.4235</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4735</v>
+        <v>-1.4078</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9222</v>
+        <v>-1.0157</v>
       </c>
       <c r="P7" t="n">
-        <v>2.0415</v>
+        <v>1.3658</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.4537</v>
+        <v>-0.2276</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4952</v>
+        <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1106</v>
+        <v>0.4169</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6261</v>
+        <v>0.4016</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4845</v>
+        <v>0.0152</v>
       </c>
       <c r="V7" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. SAKHO</t>
+          <t>A. ARANITOVIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9053</v>
+        <v>-1.7478</v>
       </c>
       <c r="E8" t="n">
-        <v>2.6917</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.597</v>
+        <v>-2.3853</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3261</v>
+        <v>-0.2821</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0146</v>
+        <v>0.3792</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3407</v>
+        <v>-0.6613</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8987</v>
+        <v>2.0384</v>
       </c>
       <c r="K8" t="n">
-        <v>1.7867</v>
+        <v>1.0407</v>
       </c>
       <c r="L8" t="n">
-        <v>0.112</v>
+        <v>0.9977</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.2248</v>
+        <v>-2.3205</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7721</v>
+        <v>-0.6615</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.4526</v>
+        <v>-1.659</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2683</v>
+        <v>-1.3658</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1901</v>
+        <v>-0.5144</v>
       </c>
       <c r="T8" t="n">
-        <v>1.8721</v>
+        <v>-0.0351</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.4793</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.5425</v>
+        <v>-1.6342</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1892</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.7317</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ARANITOVIC</t>
+          <t>J. SAKHO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0055</v>
+        <v>-1.9371</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0077</v>
+        <v>1.4724</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0132</v>
+        <v>-3.4095</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2827</v>
+        <v>-0.3299</v>
       </c>
       <c r="H9" t="n">
-        <v>0.381</v>
+        <v>1.003</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6637</v>
+        <v>-1.3329</v>
       </c>
       <c r="J9" t="n">
-        <v>2.0643</v>
+        <v>1.8764</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0594</v>
+        <v>1.7647</v>
       </c>
       <c r="L9" t="n">
-        <v>1.0048</v>
+        <v>0.1117</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.347</v>
+        <v>-2.2062</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6785</v>
+        <v>-0.7617</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.6685</v>
+        <v>-1.4446</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6805</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.361</v>
+        <v>-2.2763</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7643</v>
+        <v>0.1683</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6956</v>
+        <v>0.6965</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0687</v>
+        <v>-0.5283</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.639</v>
+        <v>-1.5479</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.1758</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.639</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3843</v>
+        <v>-2.0865</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.475</v>
+        <v>-0.3286</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9093</v>
+        <v>-1.7579</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6433</v>
+        <v>1.6346</v>
       </c>
       <c r="H10" t="n">
-        <v>2.6509</v>
+        <v>2.64</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0076</v>
+        <v>-1.0054</v>
       </c>
       <c r="J10" t="n">
-        <v>3.7109</v>
+        <v>3.683</v>
       </c>
       <c r="K10" t="n">
-        <v>3.2658</v>
+        <v>3.2438</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4451</v>
+        <v>0.4392</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.0675</v>
+        <v>-2.0483</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6149</v>
+        <v>-0.6037</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.4526</v>
+        <v>-1.4446</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3471</v>
+        <v>-1.0382</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5565</v>
+        <v>-0.3695</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7906</v>
+        <v>-0.6688</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0742</v>
+        <v>-2.9801</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1648</v>
+        <v>0.263</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.239</v>
+        <v>-3.2431</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.4506</v>
+        <v>-4.4491</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.9077</v>
+        <v>-1.9016</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.5429</v>
+        <v>-2.5474</v>
       </c>
       <c r="J11" t="n">
-        <v>0.074</v>
+        <v>0.052</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0448</v>
+        <v>0.0377</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0292</v>
+        <v>0.0142</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.5247</v>
+        <v>-4.501</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.9525</v>
+        <v>-1.9394</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.5721</v>
+        <v>-2.5617</v>
       </c>
       <c r="P11" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2114</v>
+        <v>-0.1244</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0907</v>
+        <v>0.2111</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3021</v>
+        <v>-0.3355</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.9496</v>
+        <v>-3.1853</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4234</v>
+        <v>0.1246</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.5262</v>
+        <v>-3.3098</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.5483</v>
+        <v>-3.553</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0168</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.5398</v>
+        <v>-3.5362</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2887</v>
+        <v>0.2599</v>
       </c>
       <c r="K12" t="n">
-        <v>1.7867</v>
+        <v>1.7647</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.4981</v>
+        <v>-1.5048</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.837</v>
+        <v>-3.8128</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.7953</v>
+        <v>-1.7814</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.0417</v>
+        <v>-2.0314</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R12" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.269</v>
+        <v>-0.4926</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7652</v>
+        <v>-0.1745</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5039</v>
+        <v>-0.3181</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8678</v>
+        <v>0.8603</v>
       </c>
       <c r="W12" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.3674</v>
+        <v>-5.3667</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.3746</v>
+        <v>-3.3266</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.9928</v>
+        <v>-2.0402</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.6501</v>
+        <v>-1.6502</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.6666</v>
+        <v>-0.6718</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9835</v>
+        <v>-0.9785</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3925</v>
+        <v>-0.4044</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.4298</v>
+        <v>-0.4417</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.2576</v>
+        <v>-1.2458</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2368</v>
+        <v>-0.2301</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.0209</v>
+        <v>-1.0157</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5831</v>
+        <v>-0.5783</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4869</v>
+        <v>-0.4182</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.1601</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-13.898</v>
+        <v>-13.5566</v>
       </c>
       <c r="E14" t="n">
-        <v>8.813099999999999</v>
+        <v>8.854199999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-22.7109</v>
+        <v>-22.4106</v>
       </c>
       <c r="G14" t="n">
-        <v>-16.1814</v>
+        <v>-16.1854</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4683000000000003</v>
+        <v>-0.5007999999999996</v>
       </c>
       <c r="I14" t="n">
-        <v>-15.713</v>
+        <v>-15.6844</v>
       </c>
       <c r="J14" t="n">
-        <v>13.4205</v>
+        <v>13.1928</v>
       </c>
       <c r="K14" t="n">
-        <v>11.6617</v>
+        <v>11.4973</v>
       </c>
       <c r="L14" t="n">
-        <v>1.7588</v>
+        <v>1.6953</v>
       </c>
       <c r="M14" t="n">
-        <v>-29.602</v>
+        <v>-29.3776</v>
       </c>
       <c r="N14" t="n">
-        <v>-12.1302</v>
+        <v>-11.998</v>
       </c>
       <c r="O14" t="n">
-        <v>-17.4717</v>
+        <v>-17.3799</v>
       </c>
       <c r="P14" t="n">
-        <v>6.8051</v>
+        <v>6.8291</v>
       </c>
       <c r="Q14" t="n">
-        <v>-13.6099</v>
+        <v>-13.6578</v>
       </c>
       <c r="R14" t="n">
-        <v>20.415</v>
+        <v>20.4869</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.0073</v>
+        <v>-3.6703</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3175999999999997</v>
+        <v>0.04390000000000005</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.6898</v>
+        <v>-3.7145</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5139999999999997</v>
+        <v>-0.5298999999999997</v>
       </c>
       <c r="W14" t="n">
-        <v>9.32</v>
+        <v>9.2753</v>
       </c>
       <c r="X14" t="n">
-        <v>-9.834100000000001</v>
+        <v>-9.805299999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>11.3399</v>
+        <v>9.8873</v>
       </c>
       <c r="E15" t="n">
-        <v>8.1976</v>
+        <v>7.4529</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1424</v>
+        <v>2.4343</v>
       </c>
       <c r="G15" t="n">
-        <v>4.4928</v>
+        <v>4.4952</v>
       </c>
       <c r="H15" t="n">
-        <v>3.9942</v>
+        <v>3.9869</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4985</v>
+        <v>0.5084</v>
       </c>
       <c r="J15" t="n">
-        <v>5.7279</v>
+        <v>5.6971</v>
       </c>
       <c r="K15" t="n">
-        <v>4.7204</v>
+        <v>4.6917</v>
       </c>
       <c r="L15" t="n">
-        <v>1.0076</v>
+        <v>1.0054</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2352</v>
+        <v>-1.2018</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7261</v>
+        <v>-0.7048</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.509</v>
+        <v>-0.497</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S15" t="n">
-        <v>2.9833</v>
+        <v>1.5286</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4185</v>
+        <v>0.7151</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5648</v>
+        <v>0.8135</v>
       </c>
       <c r="V15" t="n">
-        <v>2.9566</v>
+        <v>2.9529</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.9956</v>
+        <v>6.894</v>
       </c>
       <c r="E16" t="n">
-        <v>7.1772</v>
+        <v>7.0374</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1816</v>
+        <v>-0.1434</v>
       </c>
       <c r="G16" t="n">
-        <v>6.1807</v>
+        <v>6.181</v>
       </c>
       <c r="H16" t="n">
-        <v>0.45</v>
+        <v>0.4645</v>
       </c>
       <c r="I16" t="n">
-        <v>5.7308</v>
+        <v>5.7165</v>
       </c>
       <c r="J16" t="n">
-        <v>6.406</v>
+        <v>6.3803</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8139</v>
+        <v>0.8101</v>
       </c>
       <c r="L16" t="n">
-        <v>5.5921</v>
+        <v>5.5702</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2252</v>
+        <v>-0.1993</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3639</v>
+        <v>-0.3457</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4124</v>
+        <v>1.2985</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7712</v>
+        <v>0.6571</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6412</v>
+        <v>0.6415</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="17">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.3381</v>
+        <v>5.0619</v>
       </c>
       <c r="E17" t="n">
-        <v>4.1272</v>
+        <v>4.4342</v>
       </c>
       <c r="F17" t="n">
-        <v>0.211</v>
+        <v>0.6277</v>
       </c>
       <c r="G17" t="n">
-        <v>3.3379</v>
+        <v>3.3371</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0362</v>
+        <v>-1.0286</v>
       </c>
       <c r="I17" t="n">
-        <v>4.3741</v>
+        <v>4.3657</v>
       </c>
       <c r="J17" t="n">
-        <v>5.0498</v>
+        <v>5.0139</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5399</v>
+        <v>0.5236</v>
       </c>
       <c r="L17" t="n">
-        <v>4.5099</v>
+        <v>4.4903</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7119</v>
+        <v>-1.6769</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.5761</v>
+        <v>-1.5522</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1359</v>
+        <v>-0.1246</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4119</v>
+        <v>0.3183</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2934</v>
+        <v>0.0624</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1186</v>
+        <v>0.2559</v>
       </c>
       <c r="V17" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W17" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>T. SCRUBB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.0304</v>
+        <v>2.3574</v>
       </c>
       <c r="E18" t="n">
-        <v>2.9125</v>
+        <v>3.1771</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8822</v>
+        <v>-0.8197</v>
       </c>
       <c r="G18" t="n">
-        <v>4.3404</v>
+        <v>2.0773</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4804</v>
+        <v>1.1195</v>
       </c>
       <c r="I18" t="n">
-        <v>2.86</v>
+        <v>0.9579</v>
       </c>
       <c r="J18" t="n">
-        <v>4.5388</v>
+        <v>2.9938</v>
       </c>
       <c r="K18" t="n">
-        <v>2.348</v>
+        <v>1.8099</v>
       </c>
       <c r="L18" t="n">
-        <v>2.1909</v>
+        <v>1.1839</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1984</v>
+        <v>-0.9164</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8675</v>
+        <v>-0.6904</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6691</v>
+        <v>-0.226</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.722</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.4025</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4119</v>
+        <v>0.1906</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6835</v>
+        <v>0.232</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2716</v>
+        <v>-0.0414</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. SCRUBB</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.7511</v>
+        <v>2.1392</v>
       </c>
       <c r="E19" t="n">
-        <v>2.7262</v>
+        <v>2.7404</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9751</v>
+        <v>-0.6012</v>
       </c>
       <c r="G19" t="n">
-        <v>2.0649</v>
+        <v>4.3248</v>
       </c>
       <c r="H19" t="n">
-        <v>1.108</v>
+        <v>1.4819</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9569</v>
+        <v>2.8429</v>
       </c>
       <c r="J19" t="n">
-        <v>3.0097</v>
+        <v>4.4965</v>
       </c>
       <c r="K19" t="n">
-        <v>1.8183</v>
+        <v>2.3302</v>
       </c>
       <c r="L19" t="n">
-        <v>1.1914</v>
+        <v>2.1663</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9447</v>
+        <v>-0.1717</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7103</v>
+        <v>-0.8483000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2345</v>
+        <v>0.6766</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4537</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-3.4145</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4065</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2419</v>
+        <v>0.5688</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1645</v>
+        <v>-0.0229</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5463</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2913</v>
+        <v>1.6633</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1275</v>
+        <v>0.354</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1638</v>
+        <v>1.3093</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1201</v>
+        <v>1.1291</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.218</v>
+        <v>-0.2101</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3381</v>
+        <v>1.3392</v>
       </c>
       <c r="J20" t="n">
-        <v>1.6095</v>
+        <v>1.6038</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9005</v>
+        <v>0.8963</v>
       </c>
       <c r="L20" t="n">
-        <v>0.709</v>
+        <v>0.7075</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4894</v>
+        <v>-0.4747</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1185</v>
+        <v>-1.1064</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6291</v>
+        <v>0.6317</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2825</v>
+        <v>0.079</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.121</v>
+        <v>0.116</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1615</v>
+        <v>-0.037</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3209</v>
+        <v>0.7199</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3986</v>
+        <v>0.0117</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7195</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7393</v>
+        <v>0.7116</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4275</v>
+        <v>0.4034</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3118</v>
+        <v>0.3082</v>
       </c>
       <c r="J21" t="n">
-        <v>2.3006</v>
+        <v>2.2601</v>
       </c>
       <c r="K21" t="n">
-        <v>1.1838</v>
+        <v>1.1506</v>
       </c>
       <c r="L21" t="n">
-        <v>1.1168</v>
+        <v>1.1094</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5612</v>
+        <v>-1.5485</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7563</v>
+        <v>-0.7472</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.805</v>
+        <v>-0.8012</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1183</v>
+        <v>0.5609</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.121</v>
+        <v>0.3529</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2392</v>
+        <v>0.208</v>
       </c>
       <c r="V21" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,19 +2125,19 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6768</v>
+        <v>-0.675</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6768</v>
+        <v>-0.675</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5195</v>
+        <v>-0.5171</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.5195</v>
+        <v>-0.5171</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -2152,10 +2152,10 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5195</v>
+        <v>-0.5171</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5195</v>
+        <v>-0.5171</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1573</v>
+        <v>-0.1579</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1573</v>
+        <v>-0.1579</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. GIEDRAITIS</t>
+          <t>T. ABROMAITIS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8229</v>
+        <v>-1.8792</v>
       </c>
       <c r="E23" t="n">
-        <v>3.399</v>
+        <v>-0.3469</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.2219</v>
+        <v>-1.5323</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2151</v>
+        <v>-2.3442</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8298</v>
+        <v>-1.9333</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0449</v>
+        <v>-0.4109</v>
       </c>
       <c r="J23" t="n">
-        <v>2.3627</v>
+        <v>-0.0774</v>
       </c>
       <c r="K23" t="n">
-        <v>0.5715</v>
+        <v>-0.1519</v>
       </c>
       <c r="L23" t="n">
-        <v>1.7912</v>
+        <v>0.0745</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.1476</v>
+        <v>-2.2668</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.4012</v>
+        <v>-1.7814</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.7463</v>
+        <v>-0.4854</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6805</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5595</v>
+        <v>-0.626</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7168</v>
+        <v>0.0068</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1573</v>
+        <v>-0.6328</v>
       </c>
       <c r="V23" t="n">
-        <v>-3.278</v>
+        <v>1.3187</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5463</v>
+        <v>1.0895</v>
       </c>
       <c r="X23" t="n">
-        <v>-3.8243</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>T. ABROMAITIS</t>
+          <t>R. GIEDRAITIS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.3375</v>
+        <v>-2.0424</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.6871</v>
+        <v>3.1563</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6504</v>
+        <v>-5.1987</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.3567</v>
+        <v>0.2181</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.9409</v>
+        <v>-0.8246</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4158</v>
+        <v>1.0426</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.07099999999999999</v>
+        <v>2.3562</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.1456</v>
+        <v>0.5688</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0746</v>
+        <v>1.7874</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.2857</v>
+        <v>-2.1381</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.7953</v>
+        <v>-1.3934</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4904</v>
+        <v>-0.7447</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0716</v>
+        <v>0.3251</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3478</v>
+        <v>0.483</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7238</v>
+        <v>-0.1579</v>
       </c>
       <c r="V24" t="n">
-        <v>1.3176</v>
+        <v>-3.2684</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0927</v>
+        <v>0.5447</v>
       </c>
       <c r="X24" t="n">
-        <v>0.2249</v>
+        <v>-3.8132</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.7511</v>
+        <v>-3.6657</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.2194</v>
+        <v>-2.0575</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.5317</v>
+        <v>-1.6081</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.0177</v>
+        <v>-1.0142</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.2496</v>
+        <v>-1.2466</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2319</v>
+        <v>0.2324</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.0883</v>
+        <v>-0.0946</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.163</v>
+        <v>-0.1691</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.9294</v>
+        <v>-0.9196</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.0867</v>
+        <v>-1.0775</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R25" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S25" t="n">
-        <v>1.3347</v>
+        <v>0.4169</v>
       </c>
       <c r="T25" t="n">
-        <v>1.364</v>
+        <v>0.5411</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0293</v>
+        <v>-0.1242</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.5813</v>
+        <v>-6.5558</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.6511</v>
+        <v>-3.5491</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.9301</v>
+        <v>-3.0067</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.4158</v>
+        <v>-2.4135</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.1977</v>
+        <v>-1.1949</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.2181</v>
+        <v>-1.2185</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.2437</v>
+        <v>-1.2518</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.4573</v>
+        <v>-0.4621</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.1721</v>
+        <v>-1.1617</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7328</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.483</v>
+        <v>-0.461</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1391</v>
+        <v>-0.021</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3439</v>
+        <v>-0.44</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>13.8977</v>
+        <v>13.9049</v>
       </c>
       <c r="E27" t="n">
-        <v>22.711</v>
+        <v>22.4105</v>
       </c>
       <c r="F27" t="n">
-        <v>-8.8131</v>
+        <v>-8.505600000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>16.1815</v>
+        <v>16.1852</v>
       </c>
       <c r="H27" t="n">
-        <v>0.468400000000001</v>
+        <v>0.500999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>15.7131</v>
+        <v>15.6844</v>
       </c>
       <c r="J27" t="n">
-        <v>29.602</v>
+        <v>29.3779</v>
       </c>
       <c r="K27" t="n">
-        <v>12.1304</v>
+        <v>11.9981</v>
       </c>
       <c r="L27" t="n">
-        <v>17.4717</v>
+        <v>17.3798</v>
       </c>
       <c r="M27" t="n">
-        <v>-13.4203</v>
+        <v>-13.1926</v>
       </c>
       <c r="N27" t="n">
-        <v>-11.6618</v>
+        <v>-11.4972</v>
       </c>
       <c r="O27" t="n">
-        <v>-1.7587</v>
+        <v>-1.6953</v>
       </c>
       <c r="P27" t="n">
-        <v>-6.805</v>
+        <v>-6.829</v>
       </c>
       <c r="Q27" t="n">
-        <v>-20.415</v>
+        <v>-20.4869</v>
       </c>
       <c r="R27" t="n">
-        <v>13.61</v>
+        <v>13.658</v>
       </c>
       <c r="S27" t="n">
-        <v>4.0073</v>
+        <v>4.018899999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>3.689800000000001</v>
+        <v>3.7142</v>
       </c>
       <c r="U27" t="n">
-        <v>0.3173999999999999</v>
+        <v>0.3048000000000001</v>
       </c>
       <c r="V27" t="n">
-        <v>0.5139999999999998</v>
+        <v>0.5298999999999996</v>
       </c>
       <c r="W27" t="n">
-        <v>9.834000000000001</v>
+        <v>9.805199999999999</v>
       </c>
       <c r="X27" t="n">
-        <v>-9.32</v>
+        <v>-9.275400000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104541_W10.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104541_W10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104541_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104541_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104541_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104541_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104541_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104541_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104541_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104541_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104541_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104541_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104541_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104541_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-9.805299999999999</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104541_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104541_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104541_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104541_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104541_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104541_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104541_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104541_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104541_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-3.8132</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104541_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104541_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104541_W10.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-9.275400000000001</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
